--- a/output_pdfs/a_r_25_converted.xlsx
+++ b/output_pdfs/a_r_25_converted.xlsx
@@ -571,7 +571,11 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>08:10</t>
@@ -610,7 +614,11 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>08:17</t>
@@ -649,7 +657,11 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>07:44</t>
@@ -688,7 +700,11 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>07:36</t>
@@ -727,7 +743,11 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>08:27</t>
@@ -766,7 +786,11 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>08:07</t>
@@ -805,7 +829,11 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>JIX</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -844,7 +872,11 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>08:14</t>
@@ -883,7 +915,11 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>IJIA</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -922,7 +958,11 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>08:15</t>
@@ -961,7 +1001,11 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>IJIA</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>08:04</t>
@@ -1000,7 +1044,11 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>07:58</t>
@@ -1039,7 +1087,11 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>IJIA</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -1078,7 +1130,11 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>IJIX</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>08:18</t>
@@ -1117,7 +1173,11 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>IJIA</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>08:14</t>

--- a/output_pdfs/a_r_25_converted.xlsx
+++ b/output_pdfs/a_r_25_converted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח נוכחות מפורט" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח נוכחות מפורט" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,11 +571,7 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>08:10</t>
@@ -614,11 +610,7 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>08:17</t>
@@ -657,11 +649,7 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>07:44</t>
@@ -700,11 +688,7 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>07:36</t>
@@ -743,11 +727,7 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>08:27</t>
@@ -786,11 +766,7 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>08:07</t>
@@ -829,11 +805,7 @@
           <t>שלישי</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>JIX</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -872,11 +844,7 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>08:14</t>
@@ -915,11 +883,7 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>IJIA</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -958,11 +922,7 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>08:15</t>
@@ -1001,11 +961,7 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>IJIA</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>08:04</t>
@@ -1044,11 +1000,7 @@
           <t>רביעי</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>07:58</t>
@@ -1087,11 +1039,7 @@
           <t>חמישי</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>IJIA</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -1130,11 +1078,7 @@
           <t>ראשון</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>IJIX</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>08:18</t>
@@ -1173,11 +1117,7 @@
           <t>שני</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>IJIA</t>
-        </is>
-      </c>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>08:14</t>
